--- a/Data/Home/LivingRoom.AirPurifier001.xlsx
+++ b/Data/Home/LivingRoom.AirPurifier001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709279886</v>
+        <v>1711841320</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,525 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1712294381</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1712297108</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1712556720</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1712557190</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1712900428</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1712904487</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1713247549</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1713247719</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1713332501</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1713332694</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1713417259</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1713425696</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1714109438</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: off</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AirPurifier_Operation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1714113706</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LivingRoom.AirPurifier001.state: on</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
